--- a/output/pdf_financials_xlsx/MUSH.xlsx
+++ b/output/pdf_financials_xlsx/MUSH.xlsx
@@ -1216,19 +1216,19 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>1.619329</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.681553</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.378424</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.202369</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.394974</v>
       </c>
     </row>
     <row r="35">
@@ -1260,19 +1260,19 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>1.619329</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.681553</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.378424</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.202369</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.394974</v>
       </c>
     </row>
     <row r="37">
@@ -1530,13 +1530,13 @@
         <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.413582</v>
+        <v>0.035158</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.237527</v>
+        <v>0.035158</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.394974</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -3589,7 +3589,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">

--- a/output/pdf_financials_xlsx/MUSH.xlsx
+++ b/output/pdf_financials_xlsx/MUSH.xlsx
@@ -565,16 +565,16 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.020708</v>
+        <v>0.024922</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.09118800000000001</v>
+        <v>0.099508</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.122342</v>
+        <v>0.142877</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.09914199999999999</v>
+        <v>0.114736</v>
       </c>
       <c r="F7" s="1" t="inlineStr">
         <is>
@@ -637,7 +637,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.020708</v>
+        <v>0.024922</v>
       </c>
       <c r="C10" s="3" t="n">
         <v>1.573569</v>
@@ -646,7 +646,7 @@
         <v>0.909718</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.09914199999999999</v>
+        <v>0.114736</v>
       </c>
       <c r="F10" s="1" t="inlineStr">
         <is>
@@ -5839,7 +5839,11 @@
           <t>Net income (loss)</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr"/>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E58" t="inlineStr">
         <is>
           <t>-</t>
@@ -7902,7 +7906,11 @@
           <t>Office expenses</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr"/>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E109" t="inlineStr">
         <is>
           <t>-</t>
@@ -9284,7 +9292,11 @@
           <t>Office expenses</t>
         </is>
       </c>
-      <c r="D143" t="inlineStr"/>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E143" s="5" t="n">
         <v>0.004214</v>
       </c>
